--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -45402,7 +45402,7 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -45443,7 +45443,7 @@
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -45484,7 +45484,7 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -45525,7 +45525,7 @@
       </c>
       <c r="I91" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -45566,7 +45566,7 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -45607,7 +45607,7 @@
       </c>
       <c r="I93" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -45648,7 +45648,7 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -45689,7 +45689,7 @@
       </c>
       <c r="I95" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -45730,7 +45730,7 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -45771,7 +45771,7 @@
       </c>
       <c r="I97" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -45812,7 +45812,7 @@
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -45853,7 +45853,7 @@
       </c>
       <c r="I99" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -45894,7 +45894,7 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -45935,7 +45935,7 @@
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -45976,7 +45976,7 @@
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -46017,7 +46017,7 @@
       </c>
       <c r="I103" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -46058,7 +46058,7 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -46099,7 +46099,7 @@
       </c>
       <c r="I105" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -46140,7 +46140,7 @@
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -46181,7 +46181,7 @@
       </c>
       <c r="I107" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -46222,7 +46222,7 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -46263,7 +46263,7 @@
       </c>
       <c r="I109" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -46304,7 +46304,7 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -46345,7 +46345,7 @@
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -46386,7 +46386,7 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -46427,7 +46427,7 @@
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -46468,7 +46468,7 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -46509,7 +46509,7 @@
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -46550,7 +46550,7 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -46591,7 +46591,7 @@
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -46632,7 +46632,7 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -46673,7 +46673,7 @@
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -46714,7 +46714,7 @@
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -46755,7 +46755,7 @@
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -46796,7 +46796,7 @@
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -46837,7 +46837,7 @@
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -46878,7 +46878,7 @@
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -46919,7 +46919,7 @@
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -46960,7 +46960,7 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -47001,7 +47001,7 @@
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -47042,7 +47042,7 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -47083,7 +47083,7 @@
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -47124,7 +47124,7 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -47165,7 +47165,7 @@
       </c>
       <c r="I131" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -47206,7 +47206,7 @@
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -47247,7 +47247,7 @@
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -47288,7 +47288,7 @@
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -47329,7 +47329,7 @@
       </c>
       <c r="I135" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -47370,7 +47370,7 @@
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -47411,7 +47411,7 @@
       </c>
       <c r="I137" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -47452,7 +47452,7 @@
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -47493,7 +47493,7 @@
       </c>
       <c r="I139" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -47534,7 +47534,7 @@
       </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -47575,7 +47575,7 @@
       </c>
       <c r="I141" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -47616,7 +47616,7 @@
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -47657,7 +47657,7 @@
       </c>
       <c r="I143" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -47739,7 +47739,7 @@
       </c>
       <c r="I145" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -47780,7 +47780,7 @@
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -47821,7 +47821,7 @@
       </c>
       <c r="I147" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -47862,7 +47862,7 @@
       </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -47903,7 +47903,7 @@
       </c>
       <c r="I149" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -47944,7 +47944,7 @@
       </c>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -47985,7 +47985,7 @@
       </c>
       <c r="I151" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -48026,7 +48026,7 @@
       </c>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier A - review first] Suspected PBN, higher confidence: generic/anonymous name, no identifiable real-world business, school, media outlet or nonprofit behind it, and no topical or geographic connection to the clinic — the same signature as the confirmed 'TOXIC — PBN pattern' bucket, just at lower link volume (3-9 pages). Review this tier first once a backlink tool (spam score / anchor text) is funded (OFF-01); batch into the next disavow file if confirmed.</t>
         </is>
       </c>
     </row>
@@ -48067,7 +48067,7 @@
       </c>
       <c r="I153" s="14" t="inlineStr">
         <is>
-          <t>Same unrelated-topic red flags as the confirmed TOXIC-PBN bucket but at lower link volume (5-9 pages) — below the confidence bar for an automatic disavow call per this sheet's own caution. Verify with a connected backlink tool (see OFF-01) or a manual look before deciding; batch into the next disavow file if confirmed.</t>
+          <t>[Tier B - review second] Lower-confidence: resolves to an identifiable real business, school, media outlet, or nonprofit in an unrelated niche/geography. Two explanations fit equally well from domain name alone — (a) incidental/non-manipulative exposure (a hacked or auto-syndicating site linking out, not solicited by the clinic), or (b) a placement from a legacy cheap link-building/guest-post vendor, which would still violate Google's guidelines even though the site itself is legitimate. Deliberately NOT downgraded to 'No action' on domain name alone — that would risk missing a real paid-link scheme. Needs the actual linking page and anchor text (via a backlink tool, OFF-01) before a final call; lower triage priority than Tier A.</t>
         </is>
       </c>
     </row>
@@ -56069,7 +56069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
@@ -56182,6 +56182,43 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="130" customHeight="1" s="23">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Backlink Audit</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>66 'Suspicious — likely PBN' rows</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>Manually reviewed every domain in the 'Needs review' bucket individually (not just pattern-matched) and split it into two triage tiers in the Notes column so review effort goes to the highest-confidence candidates first.</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>Tier A (30 domains): generic/anonymous names, no identifiable real-world entity, same signature as the confirmed TOXIC-PBN bucket at lower volume — flagged as higher-confidence PBN candidates. Tier B (36 domains): resolve to identifiable real businesses/schools/media/nonprofits in unrelated niches — could be incidental exposure OR a legacy paid-link placement; deliberately left as 'Needs review' rather than cleared, since domain identity alone can't rule out a paid guest-post scheme. Decision column unchanged (still 'Needs review' for all 66) — this only reprioritizes the follow-up work. Also confirmed during this pass: GSC access now works via the https://drranairfan.com/ URL-prefix property (siteOwner permission); the sc-domain: property is only siteUnverifiedUser, which explains the earlier 403s and independently confirms TECH-08. DataForSEO backlink tools (spam score, referring-domain authority) are still at zero balance — a live tool is still needed to fully resolve this bucket (see OFF-01).</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>Backlink Audit tab, column I (Notes) for the 66 Suspicious rows</t>
+        </is>
+      </c>
+      <c r="G7" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>

--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -631,7 +631,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K1000"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" style="23" min="1" max="1"/>
     <col width="38" customWidth="1" style="23" min="2" max="2"/>
@@ -14410,7 +14410,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K1000"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" style="23" min="1" max="1"/>
     <col width="38" customWidth="1" style="23" min="2" max="2"/>
@@ -14919,11 +14919,15 @@
       <c r="H13" s="14" t="n"/>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J13" s="16" t="n"/>
-      <c r="K13" s="14" t="n"/>
+      <c r="K13" s="14" t="inlineStr">
+        <is>
+          <t>Verified via web search (2026-09-11) that both the ABHRS and ISHRS profiles are real and live: abhrs.org/directory/listing/rana-irfan-md and ishrs.org/doctor/594807/. Could not fetch either page directly to check the current outbound link (this environment blocks fetches to arbitrary external domains) so 'does it already link' is still unconfirmed. Drafted ready-to-send outreach emails for both in docs/seo/outreach/OFF-08-society-profile-links.md. HRSP/IBHRS/FACS profile URLs not yet located - same pattern applies once found. Needs clinic staff to actually send + confirm the link was added.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="34.5" customHeight="1" s="23">
       <c r="A14" s="11" t="inlineStr">
@@ -14964,11 +14968,15 @@
       <c r="H14" s="14" t="n"/>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J14" s="16" t="n"/>
-      <c r="K14" s="14" t="n"/>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>Title confirmed by user (2026-09-11): Immediate Past President of ABHRS. Press pitch drafted in docs/seo/outreach/OFF-09-press-pitch.md, targeting Dawn/The News/Express Tribune/Business Recorder/Geo per this row's recommendation. Two claims in the draft (HRSP presidency, procedure count) are flagged as unconfirmed and bracketed for the clinic to verify or remove before sending - not asserted on my own authority. Needs clinic staff to pick a named editor contact per outlet and actually send it.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="34.5" customHeight="1" s="23">
       <c r="A15" s="17" t="inlineStr">
@@ -28093,7 +28101,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K1000"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" style="23" min="1" max="1"/>
     <col width="38" customWidth="1" style="23" min="2" max="2"/>
@@ -41872,7 +41880,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I331"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" style="23" min="1" max="1"/>
     <col width="34" customWidth="1" style="23" min="2" max="2"/>
@@ -56069,8 +56077,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
     <col width="18" customWidth="1" style="23" min="2" max="2"/>
@@ -56214,6 +56222,43 @@
         </is>
       </c>
       <c r="G7" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="130" customHeight="1" s="23">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>Off Page SEO Issue</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>OFF-08, OFF-09</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>Prepared the two highest-trust backlink opportunities in the tracker for the clinic to execute: confirming/adding the website link on Dr. Rana Irfan's real ABHRS and ISHRS member profiles, and a press pitch on his ABHRS Immediate Past President title.</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>Verified via web search that both society profiles are real and live (URLs in the draft). Could not verify their current outbound link directly - this environment blocks fetches to external domains outside the allowed set. Wrote two ready-to-send drafts to docs/seo/outreach/: OFF-08-society-profile-links.md (emails to ABHRS + ISHRS asking them to link drranairfan.com) and OFF-09-press-pitch.md (pitch to Pakistani outlets on the ABHRS leadership story). Did not send either - that represents the clinic externally and needs to go out from the clinic's own contact, per CLAUDE.md's off-page guardrail. Two factual claims in the press pitch (HRSP presidency, procedure count) are flagged as unconfirmed rather than asserted, since only the ABHRS title was confirmed this session. Off-Page tab Status set to 'In Progress' for both rows.</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>docs/seo/outreach/OFF-08-society-profile-links.md, docs/seo/outreach/OFF-09-press-pitch.md; Off Page SEO Issue tab rows OFF-08/OFF-09 (Status + Notes)</t>
+        </is>
+      </c>
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -14874,11 +14874,15 @@
       <c r="H12" s="14" t="n"/>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J12" s="16" t="n"/>
-      <c r="K12" s="14" t="n"/>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>Verified via web search (2026-09-11) that Marham, Healthwire, InstaCare and Doctoralia are all real, currently-operating platforms; Marham already has a live 'Hair Transplant Surgeons in Islamabad' category page. Added RealSelf (realself.com) as a Tier 1 target NOT in the original recommendation - free to claim, vets medical license, globally high-authority, topically exact fit for cosmetic/hair transplant. Deprioritized Sehat Kahani - real company but rural telehealth-focused, not a cosmetic-surgery directory. Wrote ready-to-submit bio copy (short + medium) using confirmed NAP/credentials in docs/seo/outreach/OFF-07-directory-targets.md. Could not create the listings myself - every platform gates on real medical-license/identity verification, which is the point of them being worth having. Needs clinic staff to actually submit.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="34.5" customHeight="1" s="23">
       <c r="A13" s="17" t="inlineStr">
@@ -56077,7 +56081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
@@ -56264,6 +56268,43 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="140" customHeight="1" s="23">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Off Page SEO Issue</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>OFF-07</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Researched and tiered real, quality directory/listing targets for backlinks + citations (the user asked for a domain list to build backlinks on), and prepared ready-to-submit profile bio copy.</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>Verified Marham, Healthwire, InstaCare and Doctoralia are real active platforms; found Marham's live Islamabad hair-transplant category page. Identified RealSelf as a stronger Tier 1 target than anything in the original OFF-07 list - free claim, license-verified, high authority, exact topical fit, doubles as a lead-gen channel. Flagged Sehat Kahani as a poor fit (rural telehealth, not cosmetic surgery) rather than including it at equal priority. Deliberately did not produce a generic 'guest post site' list - explained to the user why that category of tactic is what caused the toxic-backlink problem just cleaned up, and pointed the genuine editorial-placement route back to OFF-09's press pitch instead. Wrote bio copy (short + medium) from confirmed credentials/NAP into docs/seo/outreach/OFF-07-directory-targets.md. Did not create any accounts - each platform requires real medical license/identity verification the clinic must complete itself.</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>docs/seo/outreach/OFF-07-directory-targets.md; Off Page SEO Issue tab row OFF-07 (Status + Notes)</t>
+        </is>
+      </c>
+      <c r="G9" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
